--- a/jogos_2025-03-04.xlsx
+++ b/jogos_2025-03-04.xlsx
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Magesi</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.5</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
         <v>3.25</v>
       </c>
       <c r="N4" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AB4" t="n">
         <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.12</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.21</v>
+        <v>2.25</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.7</v>
+        <v>1.47</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45720.60416666666</v>
@@ -1030,20 +1030,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Magesi</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.65</v>
+        <v>4.5</v>
       </c>
       <c r="M5" t="n">
         <v>3.25</v>
       </c>
       <c r="N5" t="n">
-        <v>5.8</v>
+        <v>1.8</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="T5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X5" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
         <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45720.60416666666</v>
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>ENPPI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q8" t="n">
-        <v>5.3</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="X8" t="n">
-        <v>2.08</v>
+        <v>2.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>6.11</v>
+        <v>4.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['28', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['34', '39']</t>
+          <t>['53', '66', '90+4']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.72</v>
+        <v>3.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.85</v>
+        <v>1.51</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45720.66666666666</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,109 +1546,109 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ENPPI</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T9" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="U9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="Z9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.28</v>
       </c>
-      <c r="V9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AC9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>['4', '75']</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.4</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['53', '66', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45720.66666666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.3</v>
+        <v>1.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="S10" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="T10" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.36</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AA10" t="n">
-        <v>3.4</v>
+        <v>6.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['4', '75']</t>
+          <t>['28', '76']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '39']</t>
         </is>
       </c>
       <c r="AG10" t="n">
         <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AJ10" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45720.66666666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,109 +1933,109 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['31', '53', '60']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.17</v>
       </c>
-      <c r="AC12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['53', '83']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>2.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>4.9</v>
+        <v>2.85</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="O13" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S13" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,69 +2191,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="O14" t="n">
         <v>2.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
         <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
         <v>1.3</v>
       </c>
       <c r="X14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Y14" t="n">
         <v>1.82</v>
@@ -2262,38 +2262,38 @@
         <v>1.92</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AB14" t="n">
         <v>1.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['31', '53', '60']</t>
+          <t>['14', '24', '32', '88']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,19 +2320,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.23</v>
+        <v>4.9</v>
       </c>
       <c r="M15" t="n">
-        <v>3.28</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="O15" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="P15" t="n">
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.36</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X15" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['79']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>2</v>
       </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.65</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.17</v>
       </c>
       <c r="N16" t="n">
-        <v>3.95</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3</v>
-      </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.36</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['10', '62']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH16" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X17" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['14', '24', '32', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>['6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.95</v>
+        <v>2.63</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,109 +2707,109 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="O18" t="n">
-        <v>5</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['19', '40']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.78</v>
+        <v>1.05</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>2.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.88</v>
+        <v>1.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="M19" t="n">
-        <v>3.29</v>
+        <v>3.14</v>
       </c>
       <c r="N19" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
         <v>1.5</v>
@@ -2886,37 +2886,37 @@
         <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
         <v>1.07</v>
       </c>
       <c r="W19" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X19" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AC19" t="n">
         <v>1.91</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2925,20 +2925,20 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45720.69791666666</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="M20" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N20" t="n">
         <v>2.1</v>
@@ -3006,68 +3006,68 @@
         <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.25</v>
       </c>
-      <c r="X20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.8</v>
       </c>
       <c r="AD20" t="n">
         <v>1.91</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['49', '54']</t>
+          <t>['39', '49', '71']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['66', '76', '79']</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="n">
         <v>1.25</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,22 +3120,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>2.23</v>
       </c>
       <c r="M21" t="n">
-        <v>3.47</v>
+        <v>3.27</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>3.17</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
         <v>1.44</v>
@@ -3144,10 +3144,10 @@
         <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
         <v>1.07</v>
@@ -3156,7 +3156,7 @@
         <v>1.38</v>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Y21" t="n">
         <v>2.1</v>
@@ -3165,38 +3165,38 @@
         <v>1.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.73</v>
       </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AI21" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,28 +3249,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>2.77</v>
       </c>
       <c r="M22" t="n">
-        <v>3.68</v>
+        <v>3.27</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>2.48</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
         <v>3</v>
@@ -3282,32 +3282,32 @@
         <v>1.06</v>
       </c>
       <c r="W22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.33</v>
       </c>
-      <c r="X22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AC22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD22" t="n">
         <v>1.91</v>
       </c>
-      <c r="Z22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['48', '61']</t>
+          <t>['24', '39']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3316,16 +3316,16 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,19 +3352,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -3378,55 +3378,55 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.23</v>
+        <v>5.6</v>
       </c>
       <c r="M23" t="n">
-        <v>3.17</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.27</v>
+        <v>1.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="V23" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AC23" t="n">
         <v>1.91</v>
@@ -3436,25 +3436,25 @@
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['11', '33', '79', '89']</t>
+          <t>['9', '39', '77']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>3.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.83</v>
+        <v>4.33</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3481,22 +3481,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -3507,22 +3507,22 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.96</v>
+        <v>2.49</v>
       </c>
       <c r="M24" t="n">
-        <v>3.21</v>
+        <v>3.29</v>
       </c>
       <c r="N24" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="O24" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
         <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
         <v>1.44</v>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['9', '27', '30']</t>
+          <t>['59']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.37</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="N25" t="n">
-        <v>2.9</v>
+        <v>3.47</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
         <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V25" t="n">
         <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="X25" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2</v>
       </c>
-      <c r="Z25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['12']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH25" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>['7', '71']</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>['27', '72']</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AI25" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Carlisle United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="N26" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.44</v>
@@ -3789,59 +3789,59 @@
         <v>2.63</v>
       </c>
       <c r="T26" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V26" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X26" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD26" t="n">
         <v>1.91</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,19 +3868,19 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -3894,62 +3894,62 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.96</v>
+        <v>2.53</v>
       </c>
       <c r="M27" t="n">
-        <v>3.33</v>
+        <v>3.04</v>
       </c>
       <c r="N27" t="n">
-        <v>3.84</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="P27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y27" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y27" t="n">
+      <c r="Z27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AD27" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3957,20 +3957,20 @@
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '83']</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45720.69791666666</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,22 +4023,22 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.37</v>
+        <v>4.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.36</v>
+        <v>3.47</v>
       </c>
       <c r="N28" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="O28" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="P28" t="n">
         <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="R28" t="n">
         <v>1.44</v>
@@ -4053,50 +4053,50 @@
         <v>1.33</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W28" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Z28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC28" t="n">
         <v>1.83</v>
       </c>
-      <c r="AA28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD28" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['39', '49', '71']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="n">
         <v>1.25</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.62</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,91 +4126,91 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="M29" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['24', '39']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.42</v>
+        <v>1.97</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45720.69791666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="M30" t="n">
-        <v>3.27</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>3.17</v>
+        <v>5.1</v>
       </c>
       <c r="O30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S30" t="n">
         <v>2.75</v>
       </c>
-      <c r="P30" t="n">
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>['48', '61']</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH30" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q30" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="AI30" t="n">
         <v>1.44</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45720.69791666666</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.49</v>
+        <v>3.92</v>
       </c>
       <c r="M31" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="N31" t="n">
-        <v>2.74</v>
+        <v>1.96</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T31" t="n">
         <v>3.75</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U31" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="V31" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="W31" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X31" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19', '40']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.8</v>
+        <v>2.88</v>
       </c>
       <c r="AJ31" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45720.69791666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,23 +4513,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="M32" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="N32" t="n">
-        <v>2.48</v>
+        <v>2.19</v>
       </c>
       <c r="O32" t="n">
         <v>3.75</v>
       </c>
       <c r="P32" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R32" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T32" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="W32" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="X32" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.37</v>
+        <v>1.94</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.75</v>
+        <v>3.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>1.73</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
       <c r="AG32" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45720.69791666666</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,22 +4642,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -4668,65 +4668,65 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="M33" t="n">
-        <v>3.28</v>
+        <v>3.47</v>
       </c>
       <c r="N33" t="n">
-        <v>3.47</v>
+        <v>4.5</v>
       </c>
       <c r="O33" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P33" t="n">
         <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X33" t="n">
         <v>3</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.4</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45720.69791666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,22 +4771,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.79</v>
+        <v>2.96</v>
       </c>
       <c r="M34" t="n">
-        <v>3.71</v>
+        <v>3.21</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>2.38</v>
       </c>
       <c r="O34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>['9', '27', '30']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI34" t="n">
         <v>2.5</v>
       </c>
-      <c r="P34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ34" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45720.69791666666</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,16 +4900,16 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="M35" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>3.45</v>
+        <v>3.59</v>
       </c>
       <c r="O35" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P35" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
         <v>4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T35" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U35" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V35" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W35" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
         <v>1.91</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45720.69791666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Carlisle United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M36" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T36" t="n">
         <v>3.5</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="U36" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y36" t="n">
         <v>2.05</v>
       </c>
-      <c r="O36" t="n">
-        <v>4</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T36" t="n">
-        <v>3</v>
-      </c>
-      <c r="U36" t="n">
+      <c r="Z36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
         <v>1.36</v>
       </c>
-      <c r="V36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AH36" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI36" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD36" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['22']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45720.69791666666</v>
@@ -5158,25 +5158,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="N37" t="n">
-        <v>3.59</v>
+        <v>3.27</v>
       </c>
       <c r="O37" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
         <v>4</v>
       </c>
       <c r="R37" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S37" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V37" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W37" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X37" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.65</v>
+        <v>4.33</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AC37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.8</v>
       </c>
-      <c r="AD37" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['11', '33', '79', '89']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45720.69791666666</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,109 +5287,109 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="M38" t="n">
-        <v>4</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O38" t="n">
-        <v>7</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R38" t="n">
+      <c r="U38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.3</v>
       </c>
-      <c r="S38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X38" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z38" t="n">
+      <c r="AC38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['10', '62']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH38" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>['9', '39', '77']</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AI38" t="n">
-        <v>4.33</v>
+        <v>1.44</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.22</v>
+        <v>3</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45720.69791666666</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2</v>
+      </c>
+      <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>2.37</v>
       </c>
       <c r="M39" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="O39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P39" t="n">
         <v>2.1</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q39" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T39" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="U39" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V39" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W39" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X39" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA39" t="n">
         <v>3.6</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['7', '71']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '72']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.67</v>
+        <v>1.55</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45720.69791666666</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,65 +5700,65 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.3</v>
+        <v>1.79</v>
       </c>
       <c r="M41" t="n">
-        <v>3.47</v>
+        <v>3.71</v>
       </c>
       <c r="N41" t="n">
-        <v>1.82</v>
+        <v>4.2</v>
       </c>
       <c r="O41" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="P41" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="Q41" t="n">
+        <v>4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.5</v>
       </c>
-      <c r="R41" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T41" t="n">
-        <v>3.25</v>
-      </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="V41" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB41" t="n">
         <v>1.4</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC41" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5767,16 +5767,16 @@
         </is>
       </c>
       <c r="AG41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH41" t="n">
         <v>1.8</v>
       </c>
-      <c r="AH41" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI41" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45720.69791666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,19 +5803,19 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -5832,77 +5832,77 @@
         <v>3.3</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q42" t="n">
         <v>2.4</v>
       </c>
       <c r="R42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB42" t="n">
         <v>1.36</v>
       </c>
-      <c r="S42" t="n">
-        <v>3</v>
-      </c>
-      <c r="T42" t="n">
+      <c r="AC42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>['49', '54']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>['66', '76', '79']</t>
+        </is>
+      </c>
+      <c r="AG42" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI42" t="n">
         <v>2.63</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>['90+3']</t>
-        </is>
-      </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.6</v>
       </c>
       <c r="AJ42" t="n">
         <v>1.57</v>
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,28 +5958,28 @@
         </is>
       </c>
       <c r="L43" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N43" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O43" t="n">
         <v>2.1</v>
       </c>
-      <c r="M43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.75</v>
-      </c>
       <c r="P43" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="T43" t="n">
         <v>2.75</v>
@@ -5988,53 +5988,53 @@
         <v>1.4</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AD43" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
+          <t>['16', '59']</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG43" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AJ43" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45720.70833333334</v>
@@ -6061,16 +6061,16 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -6079,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -6087,22 +6087,22 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="M44" t="n">
-        <v>3.97</v>
+        <v>3.64</v>
       </c>
       <c r="N44" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="O44" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R44" t="n">
         <v>1.36</v>
@@ -6111,59 +6111,59 @@
         <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U44" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V44" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W44" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X44" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Y44" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.8</v>
       </c>
-      <c r="Z44" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AD44" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>['4', '55']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>['32']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45720.70833333334</v>
@@ -6190,16 +6190,16 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
@@ -6208,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,22 +6216,22 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="M45" t="n">
-        <v>3.64</v>
+        <v>3.97</v>
       </c>
       <c r="N45" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O45" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R45" t="n">
         <v>1.36</v>
@@ -6240,59 +6240,59 @@
         <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.4</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X45" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AC45" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['4', '55']</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['32']</t>
+          <t>['68']</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45720.70833333334</v>
@@ -6448,22 +6448,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -6474,28 +6474,28 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>3.73</v>
+        <v>3.5</v>
       </c>
       <c r="N47" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="P47" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R47" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
         <v>2.75</v>
@@ -6504,35 +6504,35 @@
         <v>1.4</v>
       </c>
       <c r="V47" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X47" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['16', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -6541,16 +6541,16 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AJ47" t="n">
-        <v>3.75</v>
+        <v>2.4</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45720.70833333334</v>
